--- a/diseases/d214/2010-2014.xlsx
+++ b/diseases/d214/2010-2014.xlsx
@@ -6353,7 +6353,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19058,7 +19058,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21614,7 +21614,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22013,7 +22013,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -22973,7 +22973,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -23372,7 +23372,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -24170,7 +24170,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24731,7 +24731,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -25928,7 +25928,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -26888,7 +26888,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -28646,7 +28646,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29045,7 +29045,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30404,7 +30404,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30803,7 +30803,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31202,7 +31202,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31601,7 +31601,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32162,7 +32162,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32561,7 +32561,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -32960,7 +32960,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -33359,7 +33359,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34319,7 +34319,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -34718,7 +34718,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -35117,7 +35117,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35516,7 +35516,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -36077,7 +36077,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -36476,7 +36476,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -36875,7 +36875,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -37274,7 +37274,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37835,7 +37835,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -38234,7 +38234,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -38633,7 +38633,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -39032,7 +39032,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -39992,7 +39992,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -40391,7 +40391,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -40790,7 +40790,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41189,7 +41189,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41750,7 +41750,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42149,7 +42149,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -42548,7 +42548,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -42947,7 +42947,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43508,7 +43508,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -43907,7 +43907,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -44306,7 +44306,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
@@ -44705,7 +44705,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -45266,7 +45266,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -45665,7 +45665,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -46064,7 +46064,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -46463,7 +46463,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -46862,7 +46862,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47423,7 +47423,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -47822,7 +47822,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -48221,7 +48221,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -48620,7 +48620,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -49181,7 +49181,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -49580,7 +49580,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -49979,7 +49979,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -50378,7 +50378,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50777,7 +50777,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51338,7 +51338,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -51737,7 +51737,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -52136,7 +52136,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -52535,7 +52535,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -53096,7 +53096,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53495,7 +53495,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -53894,7 +53894,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -54293,7 +54293,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -54854,7 +54854,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
@@ -55253,7 +55253,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -55652,7 +55652,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -56051,7 +56051,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -56450,7 +56450,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -57011,7 +57011,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57410,7 +57410,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -57809,7 +57809,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -58208,7 +58208,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
